--- a/artfynd/A 20012-2026 artfynd.xlsx
+++ b/artfynd/A 20012-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129936566</v>
+        <v>133456847</v>
       </c>
       <c r="B2" t="n">
-        <v>91742</v>
+        <v>97435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stöllet, Vrm</t>
+          <t>Orsbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>405341</v>
+        <v>405318</v>
       </c>
       <c r="R2" t="n">
-        <v>6699596</v>
+        <v>6699618</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,44 +770,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133456842</v>
+        <v>133456848</v>
       </c>
       <c r="B3" t="n">
-        <v>91922</v>
+        <v>97435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>405307</v>
+        <v>405329</v>
       </c>
       <c r="R3" t="n">
-        <v>6699631</v>
+        <v>6699635</v>
       </c>
       <c r="S3" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -842,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -852,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133456844</v>
+        <v>133456850</v>
       </c>
       <c r="B4" t="n">
-        <v>92184</v>
+        <v>97435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>405314</v>
+        <v>405344</v>
       </c>
       <c r="R4" t="n">
-        <v>6699630</v>
+        <v>6699617</v>
       </c>
       <c r="S4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -959,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,48 +996,52 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133456845</v>
+        <v>133456853</v>
       </c>
       <c r="B5" t="n">
-        <v>92640</v>
+        <v>97435</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1965</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Citronporing</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Antrodiella citrinella</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Ryvarden</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Orsbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>405316</v>
+        <v>405346</v>
       </c>
       <c r="R5" t="n">
-        <v>6699618</v>
+        <v>6699605</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1056,7 +1070,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1066,7 +1080,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1075,6 +1089,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1093,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133456847</v>
+        <v>133456855</v>
       </c>
       <c r="B6" t="n">
-        <v>97420</v>
+        <v>97435</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1128,13 +1143,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>405318</v>
+        <v>405333</v>
       </c>
       <c r="R6" t="n">
-        <v>6699618</v>
+        <v>6699596</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1163,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1173,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133456857</v>
+        <v>133456858</v>
       </c>
       <c r="B7" t="n">
-        <v>91973</v>
+        <v>97435</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1238,10 +1253,10 @@
         <v>405350</v>
       </c>
       <c r="R7" t="n">
-        <v>6699593</v>
+        <v>6699612</v>
       </c>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1270,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1280,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,32 +1322,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133456843</v>
+        <v>133456852</v>
       </c>
       <c r="B8" t="n">
-        <v>92640</v>
+        <v>85592</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1965</v>
+        <v>241</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Citronporing</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Antrodiella citrinella</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Ryvarden</t>
+          <t>(Alb. &amp; Schwein.) Shear</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,13 +1357,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>405319</v>
+        <v>405347</v>
       </c>
       <c r="R8" t="n">
-        <v>6699620</v>
+        <v>6699608</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1377,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1387,7 +1402,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1396,6 +1411,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1414,14 +1430,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133456856</v>
+        <v>129936566</v>
       </c>
       <c r="B9" t="n">
-        <v>91973</v>
+        <v>91923</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1445,17 +1461,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Orsbäcken, Vrm</t>
+          <t>Stöllet, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>405336</v>
+        <v>405341</v>
       </c>
       <c r="R9" t="n">
-        <v>6699591</v>
+        <v>6699596</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1479,22 +1495,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>18:14</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>18:14</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1509,44 +1515,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133456855</v>
+        <v>133456854</v>
       </c>
       <c r="B10" t="n">
-        <v>97420</v>
+        <v>91988</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,13 +1562,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>405333</v>
+        <v>405342</v>
       </c>
       <c r="R10" t="n">
-        <v>6699596</v>
+        <v>6699598</v>
       </c>
       <c r="S10" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1591,7 +1597,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1601,7 +1607,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1625,6 +1631,852 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>133456856</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91988</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Orsbäcken, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>405336</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6699591</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>133456857</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91988</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Orsbäcken, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>405350</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6699593</v>
+      </c>
+      <c r="S12" t="n">
+        <v>11</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>133456859</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91988</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Orsbäcken, Vrm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>405364</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6699605</v>
+      </c>
+      <c r="S13" t="n">
+        <v>13</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>18:29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>18:29</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>133456843</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92655</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1965</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Citronporing</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Antrodiella citrinella</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Ryvarden</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Orsbäcken, Vrm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>405319</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6699620</v>
+      </c>
+      <c r="S14" t="n">
+        <v>6</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>133456845</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92655</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1965</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Citronporing</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Antrodiella citrinella</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Ryvarden</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Orsbäcken, Vrm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>405316</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6699618</v>
+      </c>
+      <c r="S15" t="n">
+        <v>8</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>133456844</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92199</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Orsbäcken, Vrm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>405314</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6699630</v>
+      </c>
+      <c r="S16" t="n">
+        <v>22</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>133456842</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91937</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Orsbäcken, Vrm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>405307</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6699631</v>
+      </c>
+      <c r="S17" t="n">
+        <v>17</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129936564</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Stöllet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>405454</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6699562</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20012-2026 artfynd.xlsx
+++ b/artfynd/A 20012-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133456847</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133456848</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133456850</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133456853</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133456855</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1319,6 +1349,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133456858</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1427,6 +1462,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133456852</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1524,6 +1564,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129936566</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1631,6 +1676,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133456854</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1738,6 +1788,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133456856</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1845,6 +1900,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133456857</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1952,6 +2012,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133456859</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2059,6 +2124,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133456843</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2166,6 +2236,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133456845</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2273,6 +2348,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133456844</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2380,6 +2460,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133456842</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2477,8 +2562,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129936564</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>